--- a/03_Outputs/Agua_Bosques_Turismo/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Agua_Bosques_Turismo/03_Ordenamiento/ordenamiento.xlsx
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="E3" s="112">
-        <v>0.413116055348241</v>
+        <v>0.41311605534824</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="E9" s="112">
-        <v>0.503491646142619</v>
+        <v>0.50349164614262</v>
       </c>
     </row>
     <row r="10">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="E10" s="112">
-        <v>0.680957830500501</v>
+        <v>0.680957830500498</v>
       </c>
     </row>
     <row r="11">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="E12" s="112">
-        <v>0.466490176108494</v>
+        <v>0.466490176108495</v>
       </c>
     </row>
     <row r="13">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.413116055348241</v>
+        <v>0.41311605534824</v>
       </c>
     </row>
     <row r="4">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.503491646142619</v>
+        <v>0.50349164614262</v>
       </c>
     </row>
     <row r="7">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.680957830500501</v>
+        <v>0.680957830500498</v>
       </c>
     </row>
     <row r="8">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.466490176108494</v>
+        <v>0.466490176108495</v>
       </c>
     </row>
   </sheetData>
